--- a/artfynd/A 44773-2021 artfynd.xlsx
+++ b/artfynd/A 44773-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44773-2021 artfynd.xlsx
+++ b/artfynd/A 44773-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1914813</v>
+        <v>293979</v>
       </c>
       <c r="B2" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79155</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>925</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Allékantlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lecanora impudens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539200.0111110681</v>
+        <v>539131</v>
       </c>
       <c r="R2" t="n">
-        <v>7060622.794137029</v>
+        <v>7060600</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2008-06-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-06-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,12 +759,15 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>i 120-årig granskog av friskfuktig lågörttyp</t>
-        </is>
+          <t>i över 120-årig granskog</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>5</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>på bark på stam av levande sälg (38 cm dbh)</t>
+          <t>5 substratenheter # på bark på stam av 5 levande aspar (28, 31, 20, 25 och 10 cm dbh)</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,37 +789,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>293979</v>
+        <v>1885706</v>
       </c>
       <c r="B3" t="n">
-        <v>77328</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>925</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Allékantlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lecanora impudens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539131.385875773</v>
+        <v>539010</v>
       </c>
       <c r="R3" t="n">
-        <v>7060599.744657745</v>
+        <v>7060293</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,19 +857,9 @@
           <t>2008-06-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-06-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,15 +873,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>i över 120-årig granskog</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>5</v>
+          <t>i 100 årig garnlavsrik granskog med rikligt med döda granar</t>
+        </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>5 substratenheter # på bark på stam av 5 levande aspar (28, 31, 20, 25 och 10 cm dbh)</t>
+          <t>på bark på stam av levande asp (30 cm dbh)</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,10 +889,235 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
+          <t>Fredrik Jonsson, Lars-Olof Grund</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Vindkraft 2008 Stamåsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1914810</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Isakmyrhögen norr om Gåsflon, ca 22 km nordost om Hammerdals kyrka, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>538998</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7060267</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2008-06-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2008-06-05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>i exponerat läge i ca 10-årig granungskog</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>1 substratenheter # på bark på stam av levande rönn (28 cm dbh)</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Fredrik Jonsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Lars-Olof Grund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Vindkraft 2008 Stamåsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1914813</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Isakmyrhögen norr om Gåsflon, ca 22 km nordost om Hammerdals kyrka, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>539200</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7060623</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2008-06-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2008-06-05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>i 120-årig granskog av friskfuktig lågörttyp</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>på bark på stam av levande sälg (38 cm dbh)</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Vindkraft 2008 Stamåsen</t>
         </is>

--- a/artfynd/A 44773-2021 artfynd.xlsx
+++ b/artfynd/A 44773-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>Vindkraft 2008 Stamåsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/293979</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
           <t>Vindkraft 2008 Stamåsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1885706</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
           <t>Vindkraft 2008 Stamåsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1914810</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,8 +1142,19 @@
           <t>Vindkraft 2008 Stamåsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1914813</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>